--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_5.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:M132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4625 +469,5925 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:22.589</t>
+          <t>2026-05-29 09:35:25.128</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421703902</v>
+        <v>1780022122807</v>
       </c>
       <c r="C2" t="n">
-        <v>88277</v>
+        <v>82361</v>
       </c>
       <c r="D2" t="n">
-        <v>-566.51</v>
+        <v>-1283.23</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>785</v>
+        <v>1560</v>
       </c>
       <c r="G2" t="n">
-        <v>73.56</v>
+        <v>252.6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2319</v>
+      </c>
+      <c r="L2" t="n">
+        <v>107</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:22.589</t>
+          <t>2026-05-29 09:35:25.129</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421704104</v>
+        <v>1780022123007</v>
       </c>
       <c r="C3" t="n">
-        <v>88403</v>
+        <v>82204</v>
       </c>
       <c r="D3" t="n">
-        <v>-412.18</v>
+        <v>-1376.07</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>785</v>
+        <v>1560</v>
       </c>
       <c r="G3" t="n">
-        <v>73.56</v>
+        <v>252.6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2121</v>
+      </c>
+      <c r="L3" t="n">
+        <v>125</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.726</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:22.590</t>
+          <t>2026-05-29 09:35:25.130</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421704305</v>
+        <v>1780022123226</v>
       </c>
       <c r="C4" t="n">
-        <v>88564</v>
+        <v>82802</v>
       </c>
       <c r="D4" t="n">
-        <v>-230.57</v>
+        <v>-709.27</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>785</v>
+        <v>1560</v>
       </c>
       <c r="G4" t="n">
-        <v>73.56</v>
+        <v>252.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1903</v>
+      </c>
+      <c r="L4" t="n">
+        <v>109</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.306</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:22.598</t>
+          <t>2026-05-29 09:35:25.131</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421704506</v>
+        <v>1780022123426</v>
       </c>
       <c r="C5" t="n">
-        <v>88723</v>
+        <v>82765</v>
       </c>
       <c r="D5" t="n">
-        <v>-60.05</v>
+        <v>-710.8</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>806</v>
+        <v>1560</v>
       </c>
       <c r="G5" t="n">
-        <v>72.81</v>
+        <v>252.6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1705</v>
+      </c>
+      <c r="L5" t="n">
+        <v>108</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.778</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:22.600</t>
+          <t>2026-05-29 09:35:25.132</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421704708</v>
+        <v>1780022123626</v>
       </c>
       <c r="C6" t="n">
-        <v>88151</v>
+        <v>82543</v>
       </c>
       <c r="D6" t="n">
-        <v>-629.04</v>
+        <v>-897.26</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>806</v>
+        <v>1560</v>
       </c>
       <c r="G6" t="n">
-        <v>72.81</v>
+        <v>252.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1506</v>
+      </c>
+      <c r="L6" t="n">
+        <v>111</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.598</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:23.024</t>
+          <t>2026-05-29 09:35:25.133</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421704909</v>
+        <v>1780022123826</v>
       </c>
       <c r="C7" t="n">
-        <v>88300</v>
+        <v>82544</v>
       </c>
       <c r="D7" t="n">
-        <v>-448.59</v>
+        <v>-851.4</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>806</v>
+        <v>1560</v>
       </c>
       <c r="G7" t="n">
-        <v>72.81</v>
+        <v>252.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1306</v>
+      </c>
+      <c r="L7" t="n">
+        <v>112</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.534</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:23.024</t>
+          <t>2026-05-29 09:35:25.209</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421705111</v>
+        <v>1780022124026</v>
       </c>
       <c r="C8" t="n">
-        <v>88439</v>
+        <v>82281</v>
       </c>
       <c r="D8" t="n">
-        <v>-287.16</v>
+        <v>-1071.83</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>806</v>
+        <v>1560</v>
       </c>
       <c r="G8" t="n">
-        <v>72.81</v>
+        <v>252.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1182</v>
+      </c>
+      <c r="L8" t="n">
+        <v>118</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.513</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:23.521</t>
+          <t>2026-05-29 09:35:25.733</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421705312</v>
+        <v>1780022124226</v>
       </c>
       <c r="C9" t="n">
-        <v>88497</v>
+        <v>81974</v>
       </c>
       <c r="D9" t="n">
-        <v>-214.8</v>
+        <v>-1325.24</v>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>825</v>
+        <v>1560</v>
       </c>
       <c r="G9" t="n">
-        <v>72.11</v>
+        <v>252.6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1505</v>
+      </c>
+      <c r="L9" t="n">
+        <v>112</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:23.523</t>
+          <t>2026-05-29 09:35:25.755</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421705513</v>
+        <v>1780022124426</v>
       </c>
       <c r="C10" t="n">
-        <v>88113</v>
+        <v>83189</v>
       </c>
       <c r="D10" t="n">
-        <v>-588.0599999999999</v>
+        <v>-43.98</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
-        <v>825</v>
+        <v>1560</v>
       </c>
       <c r="G10" t="n">
-        <v>72.11</v>
+        <v>252.6</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1327</v>
+      </c>
+      <c r="L10" t="n">
+        <v>115</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:24.043</t>
+          <t>2026-05-29 09:35:25.756</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421705715</v>
+        <v>1780022124626</v>
       </c>
       <c r="C11" t="n">
-        <v>88245</v>
+        <v>84001</v>
       </c>
       <c r="D11" t="n">
-        <v>-426.66</v>
+        <v>770.22</v>
       </c>
       <c r="E11" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
-        <v>825</v>
+        <v>3678</v>
       </c>
       <c r="G11" t="n">
-        <v>72.11</v>
+        <v>252.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1129</v>
+      </c>
+      <c r="L11" t="n">
+        <v>108</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.075</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:24.045</t>
+          <t>2026-05-29 09:35:27.811</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421705916</v>
+        <v>1780022124827</v>
       </c>
       <c r="C12" t="n">
-        <v>88526</v>
+        <v>82730</v>
       </c>
       <c r="D12" t="n">
-        <v>-124.33</v>
+        <v>-539.29</v>
       </c>
       <c r="E12" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
-        <v>685</v>
+        <v>3678</v>
       </c>
       <c r="G12" t="n">
-        <v>79.67</v>
+        <v>252.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2982</v>
+      </c>
+      <c r="L12" t="n">
+        <v>107</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:24.050</t>
+          <t>2026-05-29 09:35:27.813</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421706118</v>
+        <v>1780022125026</v>
       </c>
       <c r="C13" t="n">
-        <v>88120</v>
+        <v>83696</v>
       </c>
       <c r="D13" t="n">
-        <v>-524.11</v>
+        <v>453.67</v>
       </c>
       <c r="E13" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F13" t="n">
-        <v>685</v>
+        <v>3678</v>
       </c>
       <c r="G13" t="n">
-        <v>79.67</v>
+        <v>252.6</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2786</v>
+      </c>
+      <c r="L13" t="n">
+        <v>118</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.319</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:24.433</t>
+          <t>2026-05-29 09:35:27.815</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421706319</v>
+        <v>1780022125226</v>
       </c>
       <c r="C14" t="n">
-        <v>88187</v>
+        <v>85397</v>
       </c>
       <c r="D14" t="n">
-        <v>-430.91</v>
+        <v>2131.99</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
-        <v>685</v>
+        <v>3678</v>
       </c>
       <c r="G14" t="n">
-        <v>79.67</v>
+        <v>252.6</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2588</v>
+      </c>
+      <c r="L14" t="n">
+        <v>99</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.089</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:24.437</t>
+          <t>2026-05-29 09:35:27.816</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421706520</v>
+        <v>1780022125426</v>
       </c>
       <c r="C15" t="n">
-        <v>88298</v>
+        <v>84521</v>
       </c>
       <c r="D15" t="n">
-        <v>-298.36</v>
+        <v>1149.39</v>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>685</v>
+        <v>3678</v>
       </c>
       <c r="G15" t="n">
-        <v>79.67</v>
+        <v>252.6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2389</v>
+      </c>
+      <c r="L15" t="n">
+        <v>112</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:24.834</t>
+          <t>2026-05-29 09:35:28.102</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421706722</v>
+        <v>1780022125645</v>
       </c>
       <c r="C16" t="n">
-        <v>88526</v>
+        <v>84511</v>
       </c>
       <c r="D16" t="n">
-        <v>-55.44</v>
+        <v>1081.92</v>
       </c>
       <c r="E16" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F16" t="n">
-        <v>766</v>
+        <v>3678</v>
       </c>
       <c r="G16" t="n">
-        <v>75.15000000000001</v>
+        <v>252.6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2456</v>
+      </c>
+      <c r="L16" t="n">
+        <v>115</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.896</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:24.834</t>
+          <t>2026-05-29 09:35:28.103</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421706923</v>
+        <v>1780022125845</v>
       </c>
       <c r="C17" t="n">
-        <v>88010</v>
+        <v>84292</v>
       </c>
       <c r="D17" t="n">
-        <v>-568.67</v>
+        <v>808.83</v>
       </c>
       <c r="E17" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F17" t="n">
-        <v>766</v>
+        <v>3678</v>
       </c>
       <c r="G17" t="n">
-        <v>75.15000000000001</v>
+        <v>252.6</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2257</v>
+      </c>
+      <c r="L17" t="n">
+        <v>112</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:25.270</t>
+          <t>2026-05-29 09:35:28.104</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779421707125</v>
+        <v>1780022126045</v>
       </c>
       <c r="C18" t="n">
-        <v>88201</v>
+        <v>84074</v>
       </c>
       <c r="D18" t="n">
-        <v>-349.24</v>
+        <v>550.38</v>
       </c>
       <c r="E18" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>766</v>
+        <v>3678</v>
       </c>
       <c r="G18" t="n">
-        <v>75.15000000000001</v>
+        <v>252.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2058</v>
+      </c>
+      <c r="L18" t="n">
+        <v>105</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.839</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:25.271</t>
+          <t>2026-05-29 09:35:28.106</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779421707326</v>
+        <v>1780022126245</v>
       </c>
       <c r="C19" t="n">
-        <v>88405</v>
+        <v>84328</v>
       </c>
       <c r="D19" t="n">
-        <v>-127.77</v>
+        <v>776.87</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>766</v>
+        <v>3678</v>
       </c>
       <c r="G19" t="n">
-        <v>75.15000000000001</v>
+        <v>252.6</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1860</v>
+      </c>
+      <c r="L19" t="n">
+        <v>106</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.466</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:25.684</t>
+          <t>2026-05-29 09:35:28.108</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779421707527</v>
+        <v>1780022126445</v>
       </c>
       <c r="C20" t="n">
-        <v>88692</v>
+        <v>84175</v>
       </c>
       <c r="D20" t="n">
-        <v>165.61</v>
+        <v>585.02</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F20" t="n">
-        <v>725</v>
+        <v>3678</v>
       </c>
       <c r="G20" t="n">
-        <v>73.18000000000001</v>
+        <v>252.6</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1662</v>
+      </c>
+      <c r="L20" t="n">
+        <v>106</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.997</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:25.685</t>
+          <t>2026-05-29 09:35:28.309</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779421707729</v>
+        <v>1780022126645</v>
       </c>
       <c r="C21" t="n">
-        <v>88204</v>
+        <v>84651</v>
       </c>
       <c r="D21" t="n">
-        <v>-330.67</v>
+        <v>1031.77</v>
       </c>
       <c r="E21" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F21" t="n">
-        <v>725</v>
+        <v>3678</v>
       </c>
       <c r="G21" t="n">
-        <v>73.18000000000001</v>
+        <v>252.6</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1663</v>
+      </c>
+      <c r="L21" t="n">
+        <v>120</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.079</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:25.700</t>
+          <t>2026-05-29 09:35:28.310</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779421707930</v>
+        <v>1780022127292</v>
       </c>
       <c r="C22" t="n">
-        <v>88239</v>
+        <v>84449</v>
       </c>
       <c r="D22" t="n">
-        <v>-279.13</v>
+        <v>778.1799999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F22" t="n">
-        <v>725</v>
+        <v>3678</v>
       </c>
       <c r="G22" t="n">
-        <v>73.18000000000001</v>
+        <v>252.6</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1017</v>
+      </c>
+      <c r="L22" t="n">
+        <v>124</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.069</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:26.057</t>
+          <t>2026-05-29 09:35:29.074</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779421708132</v>
+        <v>1780022127505</v>
       </c>
       <c r="C23" t="n">
-        <v>88374</v>
+        <v>83715</v>
       </c>
       <c r="D23" t="n">
-        <v>-130.18</v>
+        <v>5.27</v>
       </c>
       <c r="E23" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F23" t="n">
-        <v>725</v>
+        <v>3678</v>
       </c>
       <c r="G23" t="n">
-        <v>73.18000000000001</v>
+        <v>252.6</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1568</v>
+      </c>
+      <c r="L23" t="n">
+        <v>107</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.133</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:26.057</t>
+          <t>2026-05-29 09:35:29.076</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779421708333</v>
+        <v>1780022127724</v>
       </c>
       <c r="C24" t="n">
-        <v>88494</v>
+        <v>82606</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.67</v>
+        <v>-1103.99</v>
       </c>
       <c r="E24" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F24" t="n">
-        <v>906</v>
+        <v>3678</v>
       </c>
       <c r="G24" t="n">
-        <v>83.16</v>
+        <v>252.6</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L24" t="n">
+        <v>109</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.591</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:26.464</t>
+          <t>2026-05-29 09:35:29.566</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779421708534</v>
+        <v>1780022127924</v>
       </c>
       <c r="C25" t="n">
-        <v>88080</v>
+        <v>83280</v>
       </c>
       <c r="D25" t="n">
-        <v>-417.48</v>
+        <v>-374.79</v>
       </c>
       <c r="E25" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F25" t="n">
-        <v>906</v>
+        <v>3678</v>
       </c>
       <c r="G25" t="n">
-        <v>83.16</v>
+        <v>252.6</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1641</v>
+      </c>
+      <c r="L25" t="n">
+        <v>114</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:26.465</t>
+          <t>2026-05-29 09:35:29.568</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779421708736</v>
+        <v>1780022128124</v>
       </c>
       <c r="C26" t="n">
-        <v>88156</v>
+        <v>84394</v>
       </c>
       <c r="D26" t="n">
-        <v>-320.61</v>
+        <v>757.95</v>
       </c>
       <c r="E26" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F26" t="n">
-        <v>906</v>
+        <v>3678</v>
       </c>
       <c r="G26" t="n">
-        <v>83.16</v>
+        <v>252.6</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1443</v>
+      </c>
+      <c r="L26" t="n">
+        <v>116</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.048</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:26.893</t>
+          <t>2026-05-29 09:35:29.570</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779421708937</v>
+        <v>1780022128324</v>
       </c>
       <c r="C27" t="n">
-        <v>88254</v>
+        <v>84927</v>
       </c>
       <c r="D27" t="n">
-        <v>-206.58</v>
+        <v>1253.05</v>
       </c>
       <c r="E27" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>906</v>
+        <v>3678</v>
       </c>
       <c r="G27" t="n">
-        <v>83.16</v>
+        <v>252.6</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1244</v>
+      </c>
+      <c r="L27" t="n">
+        <v>107</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.067</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:26.894</t>
+          <t>2026-05-29 09:35:29.571</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779421709139</v>
+        <v>1780022128524</v>
       </c>
       <c r="C28" t="n">
-        <v>88389</v>
+        <v>84631</v>
       </c>
       <c r="D28" t="n">
-        <v>-61.25</v>
+        <v>894.4</v>
       </c>
       <c r="E28" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F28" t="n">
-        <v>826</v>
+        <v>3678</v>
       </c>
       <c r="G28" t="n">
-        <v>65.48999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1046</v>
+      </c>
+      <c r="L28" t="n">
+        <v>112</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.009</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:27.425</t>
+          <t>2026-05-29 09:35:30.146</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779421709340</v>
+        <v>1780022128724</v>
       </c>
       <c r="C29" t="n">
-        <v>87848</v>
+        <v>85616</v>
       </c>
       <c r="D29" t="n">
-        <v>-599.1900000000001</v>
+        <v>1834.68</v>
       </c>
       <c r="E29" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F29" t="n">
-        <v>826</v>
+        <v>3678</v>
       </c>
       <c r="G29" t="n">
-        <v>65.48999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1421</v>
+      </c>
+      <c r="L29" t="n">
+        <v>115</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.638</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:27.451</t>
+          <t>2026-05-29 09:35:30.146</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779421709541</v>
+        <v>1780022128924</v>
       </c>
       <c r="C30" t="n">
-        <v>88053</v>
+        <v>84927</v>
       </c>
       <c r="D30" t="n">
-        <v>-364.23</v>
+        <v>1053.94</v>
       </c>
       <c r="E30" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F30" t="n">
-        <v>826</v>
+        <v>3678</v>
       </c>
       <c r="G30" t="n">
-        <v>65.48999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1222</v>
+      </c>
+      <c r="L30" t="n">
+        <v>114</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:27.736</t>
+          <t>2026-05-29 09:35:31.064</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779421709743</v>
+        <v>1780022129125</v>
       </c>
       <c r="C31" t="n">
-        <v>88174</v>
+        <v>84516</v>
       </c>
       <c r="D31" t="n">
-        <v>-225.02</v>
+        <v>590.25</v>
       </c>
       <c r="E31" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F31" t="n">
-        <v>826</v>
+        <v>3678</v>
       </c>
       <c r="G31" t="n">
-        <v>65.48999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1938</v>
+      </c>
+      <c r="L31" t="n">
+        <v>106</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.695</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:27.738</t>
+          <t>2026-05-29 09:35:31.065</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779421709944</v>
+        <v>1780022129324</v>
       </c>
       <c r="C32" t="n">
-        <v>88449</v>
+        <v>85202</v>
       </c>
       <c r="D32" t="n">
-        <v>61.23</v>
+        <v>1246.74</v>
       </c>
       <c r="E32" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F32" t="n">
-        <v>705</v>
+        <v>3678</v>
       </c>
       <c r="G32" t="n">
-        <v>69.73999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1740</v>
+      </c>
+      <c r="L32" t="n">
+        <v>122</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.853</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:28.101</t>
+          <t>2026-05-29 09:35:31.066</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779421710146</v>
+        <v>1780022129524</v>
       </c>
       <c r="C33" t="n">
-        <v>88077</v>
+        <v>85381</v>
       </c>
       <c r="D33" t="n">
-        <v>-313.83</v>
+        <v>1363.4</v>
       </c>
       <c r="E33" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F33" t="n">
-        <v>705</v>
+        <v>3678</v>
       </c>
       <c r="G33" t="n">
-        <v>69.73999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1541</v>
+      </c>
+      <c r="L33" t="n">
+        <v>108</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.836</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:28.102</t>
+          <t>2026-05-29 09:35:31.537</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779421710347</v>
+        <v>1780022129725</v>
       </c>
       <c r="C34" t="n">
-        <v>88394</v>
+        <v>86195</v>
       </c>
       <c r="D34" t="n">
-        <v>18.86</v>
+        <v>2109.23</v>
       </c>
       <c r="E34" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F34" t="n">
-        <v>705</v>
+        <v>3678</v>
       </c>
       <c r="G34" t="n">
-        <v>69.73999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1811</v>
+      </c>
+      <c r="L34" t="n">
+        <v>153</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.531</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:28.515</t>
+          <t>2026-05-29 09:35:31.538</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779421710548</v>
+        <v>1780022129924</v>
       </c>
       <c r="C35" t="n">
-        <v>88706</v>
+        <v>85800</v>
       </c>
       <c r="D35" t="n">
-        <v>329.92</v>
+        <v>1608.77</v>
       </c>
       <c r="E35" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F35" t="n">
-        <v>563</v>
+        <v>3678</v>
       </c>
       <c r="G35" t="n">
-        <v>95.06999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1613</v>
+      </c>
+      <c r="L35" t="n">
+        <v>117</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.545</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:28.522</t>
+          <t>2026-05-29 09:35:31.540</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779421710750</v>
+        <v>1780022130143</v>
       </c>
       <c r="C36" t="n">
-        <v>88257</v>
+        <v>86249</v>
       </c>
       <c r="D36" t="n">
-        <v>-135.58</v>
+        <v>1977.33</v>
       </c>
       <c r="E36" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F36" t="n">
-        <v>563</v>
+        <v>3678</v>
       </c>
       <c r="G36" t="n">
-        <v>95.06999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1395</v>
+      </c>
+      <c r="L36" t="n">
+        <v>113</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.317</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:29.054</t>
+          <t>2026-05-29 09:35:31.540</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779421710951</v>
+        <v>1780022130343</v>
       </c>
       <c r="C37" t="n">
-        <v>88272</v>
+        <v>84649</v>
       </c>
       <c r="D37" t="n">
-        <v>-113.8</v>
+        <v>278.46</v>
       </c>
       <c r="E37" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F37" t="n">
-        <v>563</v>
+        <v>3678</v>
       </c>
       <c r="G37" t="n">
-        <v>95.06999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1197</v>
+      </c>
+      <c r="L37" t="n">
+        <v>113</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.587</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:29.055</t>
+          <t>2026-05-29 09:35:32.382</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779421711153</v>
+        <v>1780022130543</v>
       </c>
       <c r="C38" t="n">
-        <v>88389</v>
+        <v>85620</v>
       </c>
       <c r="D38" t="n">
-        <v>8.890000000000001</v>
+        <v>1235.54</v>
       </c>
       <c r="E38" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F38" t="n">
-        <v>563</v>
+        <v>3678</v>
       </c>
       <c r="G38" t="n">
-        <v>95.06999999999999</v>
+        <v>252.6</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1837</v>
+      </c>
+      <c r="L38" t="n">
+        <v>109</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:29.331</t>
+          <t>2026-05-29 09:35:32.384</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779421711354</v>
+        <v>1780022130743</v>
       </c>
       <c r="C39" t="n">
-        <v>88591</v>
+        <v>85363</v>
       </c>
       <c r="D39" t="n">
-        <v>210.45</v>
+        <v>916.76</v>
       </c>
       <c r="E39" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F39" t="n">
-        <v>907</v>
+        <v>3678</v>
       </c>
       <c r="G39" t="n">
-        <v>105.96</v>
+        <v>252.6</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1640</v>
+      </c>
+      <c r="L39" t="n">
+        <v>116</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.993</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:29.332</t>
+          <t>2026-05-29 09:35:32.386</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779421711555</v>
+        <v>1780022130943</v>
       </c>
       <c r="C40" t="n">
-        <v>88099</v>
+        <v>85581</v>
       </c>
       <c r="D40" t="n">
-        <v>-292.07</v>
+        <v>1088.92</v>
       </c>
       <c r="E40" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F40" t="n">
-        <v>907</v>
+        <v>3678</v>
       </c>
       <c r="G40" t="n">
-        <v>105.96</v>
+        <v>252.6</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1442</v>
+      </c>
+      <c r="L40" t="n">
+        <v>90</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.967</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:29.766</t>
+          <t>2026-05-29 09:35:32.388</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779421711757</v>
+        <v>1780022131143</v>
       </c>
       <c r="C41" t="n">
-        <v>88201</v>
+        <v>85245</v>
       </c>
       <c r="D41" t="n">
-        <v>-175.47</v>
+        <v>698.48</v>
       </c>
       <c r="E41" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F41" t="n">
-        <v>907</v>
+        <v>3678</v>
       </c>
       <c r="G41" t="n">
-        <v>105.96</v>
+        <v>252.6</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1244</v>
+      </c>
+      <c r="L41" t="n">
+        <v>108</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.873</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:29.767</t>
+          <t>2026-05-29 09:35:33.822</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779421711958</v>
+        <v>1780022131343</v>
       </c>
       <c r="C42" t="n">
-        <v>88452</v>
+        <v>85236</v>
       </c>
       <c r="D42" t="n">
-        <v>84.3</v>
+        <v>654.55</v>
       </c>
       <c r="E42" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F42" t="n">
-        <v>907</v>
+        <v>3678</v>
       </c>
       <c r="G42" t="n">
-        <v>105.96</v>
+        <v>252.6</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2478</v>
+      </c>
+      <c r="L42" t="n">
+        <v>113</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.185</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:30.157</t>
+          <t>2026-05-29 09:35:33.823</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779421712160</v>
+        <v>1780022131543</v>
       </c>
       <c r="C43" t="n">
-        <v>88278</v>
+        <v>84962</v>
       </c>
       <c r="D43" t="n">
-        <v>-93.91</v>
+        <v>347.83</v>
       </c>
       <c r="E43" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F43" t="n">
-        <v>725</v>
+        <v>3678</v>
       </c>
       <c r="G43" t="n">
-        <v>106.11</v>
+        <v>252.6</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2279</v>
+      </c>
+      <c r="L43" t="n">
+        <v>113</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.953</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:30.158</t>
+          <t>2026-05-29 09:35:33.825</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779421712361</v>
+        <v>1780022131743</v>
       </c>
       <c r="C44" t="n">
-        <v>88161</v>
+        <v>85270</v>
       </c>
       <c r="D44" t="n">
-        <v>-206.22</v>
+        <v>638.4299999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F44" t="n">
-        <v>725</v>
+        <v>3678</v>
       </c>
       <c r="G44" t="n">
-        <v>106.11</v>
+        <v>252.6</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2080</v>
+      </c>
+      <c r="L44" t="n">
+        <v>108</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.738</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:30.565</t>
+          <t>2026-05-29 09:35:33.827</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779421712562</v>
+        <v>1780022131943</v>
       </c>
       <c r="C45" t="n">
-        <v>88170</v>
+        <v>86217</v>
       </c>
       <c r="D45" t="n">
-        <v>-186.91</v>
+        <v>1553.51</v>
       </c>
       <c r="E45" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F45" t="n">
-        <v>725</v>
+        <v>7437</v>
       </c>
       <c r="G45" t="n">
-        <v>106.11</v>
+        <v>252.6</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1882</v>
+      </c>
+      <c r="L45" t="n">
+        <v>111</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.405</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:30.574</t>
+          <t>2026-05-29 09:35:33.828</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779421712764</v>
+        <v>1780022132162</v>
       </c>
       <c r="C46" t="n">
-        <v>88416</v>
+        <v>85769</v>
       </c>
       <c r="D46" t="n">
-        <v>68.44</v>
+        <v>1027.84</v>
       </c>
       <c r="E46" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F46" t="n">
-        <v>725</v>
+        <v>7437</v>
       </c>
       <c r="G46" t="n">
-        <v>106.11</v>
+        <v>252.6</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1665</v>
+      </c>
+      <c r="L46" t="n">
+        <v>114</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:30.977</t>
+          <t>2026-05-29 09:35:33.829</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779421712965</v>
+        <v>1780022132362</v>
       </c>
       <c r="C47" t="n">
-        <v>88069</v>
+        <v>85272</v>
       </c>
       <c r="D47" t="n">
-        <v>-281.98</v>
+        <v>479.45</v>
       </c>
       <c r="E47" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F47" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G47" t="n">
-        <v>104.27</v>
+        <v>252.6</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1466</v>
+      </c>
+      <c r="L47" t="n">
+        <v>110</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.93</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:30.978</t>
+          <t>2026-05-29 09:35:33.830</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779421713167</v>
+        <v>1780022132562</v>
       </c>
       <c r="C48" t="n">
-        <v>88220</v>
+        <v>84814</v>
       </c>
       <c r="D48" t="n">
-        <v>-116.88</v>
+        <v>-2.53</v>
       </c>
       <c r="E48" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F48" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G48" t="n">
-        <v>104.27</v>
+        <v>252.6</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1268</v>
+      </c>
+      <c r="L48" t="n">
+        <v>113</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.664</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:31.385</t>
+          <t>2026-05-29 09:35:33.833</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779421713368</v>
+        <v>1780022132762</v>
       </c>
       <c r="C49" t="n">
-        <v>88044</v>
+        <v>86924</v>
       </c>
       <c r="D49" t="n">
-        <v>-287.04</v>
+        <v>2107.6</v>
       </c>
       <c r="E49" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F49" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G49" t="n">
-        <v>104.27</v>
+        <v>252.6</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1070</v>
+      </c>
+      <c r="L49" t="n">
+        <v>112</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.268</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:31.385</t>
+          <t>2026-05-29 09:35:34.143</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779421713569</v>
+        <v>1780022132962</v>
       </c>
       <c r="C50" t="n">
-        <v>88123</v>
+        <v>86642</v>
       </c>
       <c r="D50" t="n">
-        <v>-193.69</v>
+        <v>1720.22</v>
       </c>
       <c r="E50" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F50" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G50" t="n">
-        <v>104.27</v>
+        <v>252.6</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1180</v>
+      </c>
+      <c r="L50" t="n">
+        <v>108</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.9320000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:31.810</t>
+          <t>2026-05-29 09:35:34.543</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779421713771</v>
+        <v>1780022133162</v>
       </c>
       <c r="C51" t="n">
-        <v>87727</v>
+        <v>85339</v>
       </c>
       <c r="D51" t="n">
-        <v>-580</v>
+        <v>331.21</v>
       </c>
       <c r="E51" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F51" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G51" t="n">
-        <v>104.27</v>
+        <v>252.6</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J51" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1379</v>
+      </c>
+      <c r="L51" t="n">
+        <v>113</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.121</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:31.812</t>
+          <t>2026-05-29 09:35:34.544</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779421713972</v>
+        <v>1780022133442</v>
       </c>
       <c r="C52" t="n">
-        <v>87516</v>
+        <v>85228</v>
       </c>
       <c r="D52" t="n">
-        <v>-762</v>
+        <v>203.65</v>
       </c>
       <c r="E52" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F52" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G52" t="n">
-        <v>104.27</v>
+        <v>252.6</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1101</v>
+      </c>
+      <c r="L52" t="n">
+        <v>118</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.048</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:32.221</t>
+          <t>2026-05-29 09:35:34.546</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779421714173</v>
+        <v>1780022133642</v>
       </c>
       <c r="C53" t="n">
-        <v>88186</v>
+        <v>85592</v>
       </c>
       <c r="D53" t="n">
-        <v>-53.9</v>
+        <v>557.47</v>
       </c>
       <c r="E53" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F53" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G53" t="n">
-        <v>104.27</v>
+        <v>252.6</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K53" t="n">
+        <v>903</v>
+      </c>
+      <c r="L53" t="n">
+        <v>117</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.261</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:32.227</t>
+          <t>2026-05-29 09:35:34.929</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779421714375</v>
+        <v>1780022133842</v>
       </c>
       <c r="C54" t="n">
-        <v>88051</v>
+        <v>85171</v>
       </c>
       <c r="D54" t="n">
-        <v>-186.21</v>
+        <v>108.59</v>
       </c>
       <c r="E54" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F54" t="n">
-        <v>1490</v>
+        <v>7437</v>
       </c>
       <c r="G54" t="n">
-        <v>249.77</v>
+        <v>252.6</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1086</v>
+      </c>
+      <c r="L54" t="n">
+        <v>111</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.864</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:32.617</t>
+          <t>2026-05-29 09:35:34.930</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779421714576</v>
+        <v>1780022134042</v>
       </c>
       <c r="C55" t="n">
-        <v>87765</v>
+        <v>84807</v>
       </c>
       <c r="D55" t="n">
-        <v>-462.9</v>
+        <v>-260.84</v>
       </c>
       <c r="E55" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F55" t="n">
-        <v>1490</v>
+        <v>7437</v>
       </c>
       <c r="G55" t="n">
-        <v>249.77</v>
+        <v>252.6</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>887</v>
+      </c>
+      <c r="L55" t="n">
+        <v>116</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.548</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:32.618</t>
+          <t>2026-05-29 09:35:35.678</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779421714778</v>
+        <v>1780022134243</v>
       </c>
       <c r="C56" t="n">
-        <v>87928</v>
+        <v>85015</v>
       </c>
       <c r="D56" t="n">
-        <v>-276.75</v>
+        <v>-39.8</v>
       </c>
       <c r="E56" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F56" t="n">
-        <v>1490</v>
+        <v>7437</v>
       </c>
       <c r="G56" t="n">
-        <v>249.77</v>
+        <v>252.6</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1434</v>
+      </c>
+      <c r="L56" t="n">
+        <v>106</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.915</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:33.042</t>
+          <t>2026-05-29 09:35:35.680</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779421714979</v>
+        <v>1780022134461</v>
       </c>
       <c r="C57" t="n">
-        <v>88148</v>
+        <v>84924</v>
       </c>
       <c r="D57" t="n">
-        <v>-42.91</v>
+        <v>-128.81</v>
       </c>
       <c r="E57" t="n">
         <v>72</v>
       </c>
       <c r="F57" t="n">
-        <v>645</v>
+        <v>7437</v>
       </c>
       <c r="G57" t="n">
-        <v>256.58</v>
+        <v>252.6</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1218</v>
+      </c>
+      <c r="L57" t="n">
+        <v>118</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.689</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:33.061</t>
+          <t>2026-05-29 09:35:36.367</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779421715180</v>
+        <v>1780022134661</v>
       </c>
       <c r="C58" t="n">
-        <v>87613</v>
+        <v>86040</v>
       </c>
       <c r="D58" t="n">
-        <v>-575.77</v>
+        <v>993.63</v>
       </c>
       <c r="E58" t="n">
         <v>72</v>
       </c>
       <c r="F58" t="n">
-        <v>645</v>
+        <v>7437</v>
       </c>
       <c r="G58" t="n">
-        <v>256.58</v>
+        <v>252.6</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1705</v>
+      </c>
+      <c r="L58" t="n">
+        <v>111</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.209</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:33.433</t>
+          <t>2026-05-29 09:35:36.368</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779421715382</v>
+        <v>1780022134861</v>
       </c>
       <c r="C59" t="n">
-        <v>87870</v>
+        <v>85479</v>
       </c>
       <c r="D59" t="n">
-        <v>-289.98</v>
+        <v>382.95</v>
       </c>
       <c r="E59" t="n">
         <v>72</v>
       </c>
       <c r="F59" t="n">
-        <v>645</v>
+        <v>7437</v>
       </c>
       <c r="G59" t="n">
-        <v>256.58</v>
+        <v>252.6</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1507</v>
+      </c>
+      <c r="L59" t="n">
+        <v>118</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.779</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:33.435</t>
+          <t>2026-05-29 09:35:36.369</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779421715583</v>
+        <v>1780022135061</v>
       </c>
       <c r="C60" t="n">
-        <v>88141</v>
+        <v>83799</v>
       </c>
       <c r="D60" t="n">
-        <v>-4.48</v>
+        <v>-1316.19</v>
       </c>
       <c r="E60" t="n">
         <v>72</v>
       </c>
       <c r="F60" t="n">
-        <v>645</v>
+        <v>7437</v>
       </c>
       <c r="G60" t="n">
-        <v>256.58</v>
+        <v>252.6</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1308</v>
+      </c>
+      <c r="L60" t="n">
+        <v>109</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.774</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:33.858</t>
+          <t>2026-05-29 09:35:36.964</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779421715785</v>
+        <v>1780022135262</v>
       </c>
       <c r="C61" t="n">
-        <v>88324</v>
+        <v>84454</v>
       </c>
       <c r="D61" t="n">
-        <v>178.74</v>
+        <v>-595.38</v>
       </c>
       <c r="E61" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F61" t="n">
-        <v>665</v>
+        <v>7437</v>
       </c>
       <c r="G61" t="n">
-        <v>259.92</v>
+        <v>252.6</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1701</v>
+      </c>
+      <c r="L61" t="n">
+        <v>107</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.962</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:33.859</t>
+          <t>2026-05-29 09:35:36.965</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779421715986</v>
+        <v>1780022135461</v>
       </c>
       <c r="C62" t="n">
-        <v>87846</v>
+        <v>84843</v>
       </c>
       <c r="D62" t="n">
-        <v>-308.19</v>
+        <v>-176.62</v>
       </c>
       <c r="E62" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F62" t="n">
-        <v>665</v>
+        <v>7437</v>
       </c>
       <c r="G62" t="n">
-        <v>259.92</v>
+        <v>252.6</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1503</v>
+      </c>
+      <c r="L62" t="n">
+        <v>121</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.921</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:34.265</t>
+          <t>2026-05-29 09:35:36.966</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779421716187</v>
+        <v>1780022135661</v>
       </c>
       <c r="C63" t="n">
-        <v>88204</v>
+        <v>85054</v>
       </c>
       <c r="D63" t="n">
-        <v>65.22</v>
+        <v>43.22</v>
       </c>
       <c r="E63" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F63" t="n">
-        <v>665</v>
+        <v>7437</v>
       </c>
       <c r="G63" t="n">
-        <v>259.92</v>
+        <v>252.6</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1304</v>
+      </c>
+      <c r="L63" t="n">
+        <v>107</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.803</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:34.302</t>
+          <t>2026-05-29 09:35:36.967</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779421716389</v>
+        <v>1780022135861</v>
       </c>
       <c r="C64" t="n">
-        <v>88338</v>
+        <v>84819</v>
       </c>
       <c r="D64" t="n">
-        <v>195.95</v>
+        <v>-193.95</v>
       </c>
       <c r="E64" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F64" t="n">
-        <v>664</v>
+        <v>7437</v>
       </c>
       <c r="G64" t="n">
-        <v>262.46</v>
+        <v>252.6</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1105</v>
+      </c>
+      <c r="L64" t="n">
+        <v>109</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:34.832</t>
+          <t>2026-05-29 09:35:37.592</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779421716590</v>
+        <v>1780022136061</v>
       </c>
       <c r="C65" t="n">
-        <v>87856</v>
+        <v>83862</v>
       </c>
       <c r="D65" t="n">
-        <v>-295.84</v>
+        <v>-1141.25</v>
       </c>
       <c r="E65" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F65" t="n">
-        <v>664</v>
+        <v>7437</v>
       </c>
       <c r="G65" t="n">
-        <v>262.46</v>
+        <v>252.6</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1530</v>
+      </c>
+      <c r="L65" t="n">
+        <v>115</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.033</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:34.841</t>
+          <t>2026-05-29 09:35:37.598</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779421716792</v>
+        <v>1780022136261</v>
       </c>
       <c r="C66" t="n">
-        <v>88064</v>
+        <v>83989</v>
       </c>
       <c r="D66" t="n">
-        <v>-73.05</v>
+        <v>-957.1900000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F66" t="n">
-        <v>664</v>
+        <v>7437</v>
       </c>
       <c r="G66" t="n">
-        <v>262.46</v>
+        <v>252.6</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1336</v>
+      </c>
+      <c r="L66" t="n">
+        <v>107</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.114</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:35.140</t>
+          <t>2026-05-29 09:35:37.600</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779421716993</v>
+        <v>1780022136461</v>
       </c>
       <c r="C67" t="n">
-        <v>88273</v>
+        <v>84833</v>
       </c>
       <c r="D67" t="n">
-        <v>139.6</v>
+        <v>-65.33</v>
       </c>
       <c r="E67" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F67" t="n">
-        <v>664</v>
+        <v>7437</v>
       </c>
       <c r="G67" t="n">
-        <v>262.46</v>
+        <v>252.6</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1138</v>
+      </c>
+      <c r="L67" t="n">
+        <v>107</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.947</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:35.141</t>
+          <t>2026-05-29 09:35:37.601</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779421717195</v>
+        <v>1780022136680</v>
       </c>
       <c r="C68" t="n">
-        <v>88332</v>
+        <v>86548</v>
       </c>
       <c r="D68" t="n">
-        <v>191.62</v>
+        <v>1652.94</v>
       </c>
       <c r="E68" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F68" t="n">
-        <v>766</v>
+        <v>7437</v>
       </c>
       <c r="G68" t="n">
-        <v>262.42</v>
+        <v>252.6</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K68" t="n">
+        <v>920</v>
+      </c>
+      <c r="L68" t="n">
+        <v>108</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.902</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:35.141</t>
+          <t>2026-05-29 09:35:38.081</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779421717396</v>
+        <v>1780022136880</v>
       </c>
       <c r="C69" t="n">
-        <v>87846</v>
+        <v>86002</v>
       </c>
       <c r="D69" t="n">
-        <v>-303.96</v>
+        <v>1024.29</v>
       </c>
       <c r="E69" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F69" t="n">
-        <v>766</v>
+        <v>7437</v>
       </c>
       <c r="G69" t="n">
-        <v>262.42</v>
+        <v>252.6</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L69" t="n">
+        <v>95</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:35.496</t>
+          <t>2026-05-29 09:35:38.633</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779421717597</v>
+        <v>1780022137080</v>
       </c>
       <c r="C70" t="n">
-        <v>88056</v>
+        <v>85979</v>
       </c>
       <c r="D70" t="n">
-        <v>-78.76000000000001</v>
+        <v>950.08</v>
       </c>
       <c r="E70" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F70" t="n">
-        <v>766</v>
+        <v>7437</v>
       </c>
       <c r="G70" t="n">
-        <v>262.42</v>
+        <v>252.6</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J70" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1551</v>
+      </c>
+      <c r="L70" t="n">
+        <v>112</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.644</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:35.907</t>
+          <t>2026-05-29 09:35:38.649</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779421717799</v>
+        <v>1780022137320</v>
       </c>
       <c r="C71" t="n">
-        <v>88249</v>
+        <v>87689</v>
       </c>
       <c r="D71" t="n">
-        <v>118.18</v>
+        <v>2612.57</v>
       </c>
       <c r="E71" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F71" t="n">
-        <v>766</v>
+        <v>7437</v>
       </c>
       <c r="G71" t="n">
-        <v>262.42</v>
+        <v>252.6</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>36.47</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1328</v>
+      </c>
+      <c r="L71" t="n">
+        <v>126</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.676</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:35.909</t>
+          <t>2026-05-29 09:35:38.650</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779421718000</v>
+        <v>1780022137520</v>
       </c>
       <c r="C72" t="n">
-        <v>88231</v>
+        <v>87958</v>
       </c>
       <c r="D72" t="n">
-        <v>94.27</v>
+        <v>2750.95</v>
       </c>
       <c r="E72" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F72" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G72" t="n">
-        <v>260.7</v>
+        <v>252.6</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1129</v>
+      </c>
+      <c r="L72" t="n">
+        <v>123</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.008</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:36.293</t>
+          <t>2026-05-29 09:35:39.473</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779421718202</v>
+        <v>1780022137721</v>
       </c>
       <c r="C73" t="n">
-        <v>88213</v>
+        <v>87116</v>
       </c>
       <c r="D73" t="n">
-        <v>71.55</v>
+        <v>1771.4</v>
       </c>
       <c r="E73" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F73" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G73" t="n">
-        <v>260.7</v>
+        <v>252.6</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L73" t="n">
+        <v>108</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.872</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:36.294</t>
+          <t>2026-05-29 09:35:39.475</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779421718403</v>
+        <v>1780022137920</v>
       </c>
       <c r="C74" t="n">
-        <v>88357</v>
+        <v>86651</v>
       </c>
       <c r="D74" t="n">
-        <v>211.98</v>
+        <v>1217.83</v>
       </c>
       <c r="E74" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F74" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G74" t="n">
-        <v>260.7</v>
+        <v>252.6</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1553</v>
+      </c>
+      <c r="L74" t="n">
+        <v>112</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.623</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:36.818</t>
+          <t>2026-05-29 09:35:41.294</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779421718604</v>
+        <v>1780022138120</v>
       </c>
       <c r="C75" t="n">
-        <v>88686</v>
+        <v>84889</v>
       </c>
       <c r="D75" t="n">
-        <v>530.38</v>
+        <v>-605.0599999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F75" t="n">
-        <v>604</v>
+        <v>7437</v>
       </c>
       <c r="G75" t="n">
-        <v>256.86</v>
+        <v>252.6</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3172</v>
+      </c>
+      <c r="L75" t="n">
+        <v>119</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.594</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:36.819</t>
+          <t>2026-05-29 09:35:41.295</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779421718806</v>
+        <v>1780022138320</v>
       </c>
       <c r="C76" t="n">
-        <v>88319</v>
+        <v>84376</v>
       </c>
       <c r="D76" t="n">
-        <v>136.86</v>
+        <v>-1087.81</v>
       </c>
       <c r="E76" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F76" t="n">
-        <v>604</v>
+        <v>7437</v>
       </c>
       <c r="G76" t="n">
-        <v>256.86</v>
+        <v>252.6</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2974</v>
+      </c>
+      <c r="L76" t="n">
+        <v>106</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.853</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:37.130</t>
+          <t>2026-05-29 09:35:41.296</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779421719007</v>
+        <v>1780022138520</v>
       </c>
       <c r="C77" t="n">
-        <v>88621</v>
+        <v>84636</v>
       </c>
       <c r="D77" t="n">
-        <v>432.02</v>
+        <v>-773.42</v>
       </c>
       <c r="E77" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F77" t="n">
-        <v>604</v>
+        <v>7437</v>
       </c>
       <c r="G77" t="n">
-        <v>256.86</v>
+        <v>252.6</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2775</v>
+      </c>
+      <c r="L77" t="n">
+        <v>104</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.048</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:37.130</t>
+          <t>2026-05-29 09:35:41.298</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779421719209</v>
+        <v>1780022138739</v>
       </c>
       <c r="C78" t="n">
-        <v>88800</v>
+        <v>84639</v>
       </c>
       <c r="D78" t="n">
-        <v>589.42</v>
+        <v>-731.75</v>
       </c>
       <c r="E78" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F78" t="n">
-        <v>604</v>
+        <v>7437</v>
       </c>
       <c r="G78" t="n">
-        <v>261.15</v>
+        <v>252.6</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2558</v>
+      </c>
+      <c r="L78" t="n">
+        <v>116</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:37.789</t>
+          <t>2026-05-29 09:35:41.299</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779421719410</v>
+        <v>1780022138939</v>
       </c>
       <c r="C79" t="n">
-        <v>88666</v>
+        <v>85544</v>
       </c>
       <c r="D79" t="n">
-        <v>425.94</v>
+        <v>209.84</v>
       </c>
       <c r="E79" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F79" t="n">
-        <v>604</v>
+        <v>7437</v>
       </c>
       <c r="G79" t="n">
-        <v>261.15</v>
+        <v>252.6</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2359</v>
+      </c>
+      <c r="L79" t="n">
+        <v>114</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.881</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:37.815</t>
+          <t>2026-05-29 09:35:41.300</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779421719611</v>
+        <v>1780022139139</v>
       </c>
       <c r="C80" t="n">
-        <v>88702</v>
+        <v>84462</v>
       </c>
       <c r="D80" t="n">
-        <v>440.65</v>
+        <v>-882.65</v>
       </c>
       <c r="E80" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F80" t="n">
-        <v>604</v>
+        <v>7437</v>
       </c>
       <c r="G80" t="n">
-        <v>261.15</v>
+        <v>252.6</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2160</v>
+      </c>
+      <c r="L80" t="n">
+        <v>112</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:37.819</t>
+          <t>2026-05-29 09:35:41.301</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779421719813</v>
+        <v>1780022139339</v>
       </c>
       <c r="C81" t="n">
-        <v>88816</v>
+        <v>83263</v>
       </c>
       <c r="D81" t="n">
-        <v>532.61</v>
+        <v>-2037.52</v>
       </c>
       <c r="E81" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F81" t="n">
-        <v>604</v>
+        <v>7437</v>
       </c>
       <c r="G81" t="n">
-        <v>261.15</v>
+        <v>252.6</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1961</v>
+      </c>
+      <c r="L81" t="n">
+        <v>103</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.831</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:37.836</t>
+          <t>2026-05-29 09:35:41.302</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779421720014</v>
+        <v>1780022139539</v>
       </c>
       <c r="C82" t="n">
-        <v>89049</v>
+        <v>85515</v>
       </c>
       <c r="D82" t="n">
-        <v>738.98</v>
+        <v>316.36</v>
       </c>
       <c r="E82" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F82" t="n">
-        <v>786</v>
+        <v>7437</v>
       </c>
       <c r="G82" t="n">
-        <v>260.61</v>
+        <v>252.6</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1762</v>
+      </c>
+      <c r="L82" t="n">
+        <v>108</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:38.137</t>
+          <t>2026-05-29 09:35:41.575</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779421720216</v>
+        <v>1780022139739</v>
       </c>
       <c r="C83" t="n">
-        <v>88722</v>
+        <v>85365</v>
       </c>
       <c r="D83" t="n">
-        <v>375.03</v>
+        <v>150.54</v>
       </c>
       <c r="E83" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F83" t="n">
-        <v>786</v>
+        <v>7437</v>
       </c>
       <c r="G83" t="n">
-        <v>260.61</v>
+        <v>252.6</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1835</v>
+      </c>
+      <c r="L83" t="n">
+        <v>107</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:38.139</t>
+          <t>2026-05-29 09:35:43.549</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779421720417</v>
+        <v>1780022139939</v>
       </c>
       <c r="C84" t="n">
-        <v>88901</v>
+        <v>87406</v>
       </c>
       <c r="D84" t="n">
-        <v>535.28</v>
+        <v>2184.01</v>
       </c>
       <c r="E84" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="F84" t="n">
-        <v>786</v>
+        <v>7437</v>
       </c>
       <c r="G84" t="n">
-        <v>260.61</v>
+        <v>252.6</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J84" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K84" t="n">
+        <v>3609</v>
+      </c>
+      <c r="L84" t="n">
+        <v>115</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.694</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:38.620</t>
+          <t>2026-05-29 09:35:43.585</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779421720618</v>
+        <v>1780022140800</v>
       </c>
       <c r="C85" t="n">
-        <v>89092</v>
+        <v>87380</v>
       </c>
       <c r="D85" t="n">
-        <v>699.52</v>
+        <v>2048.81</v>
       </c>
       <c r="E85" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F85" t="n">
-        <v>765</v>
+        <v>7437</v>
       </c>
       <c r="G85" t="n">
-        <v>260.63</v>
+        <v>252.6</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K85" t="n">
+        <v>2785</v>
+      </c>
+      <c r="L85" t="n">
+        <v>123</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:38.635</t>
+          <t>2026-05-29 09:35:43.586</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779421720820</v>
+        <v>1780022141018</v>
       </c>
       <c r="C86" t="n">
-        <v>89188</v>
+        <v>87391</v>
       </c>
       <c r="D86" t="n">
-        <v>760.54</v>
+        <v>1957.37</v>
       </c>
       <c r="E86" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F86" t="n">
-        <v>765</v>
+        <v>7437</v>
       </c>
       <c r="G86" t="n">
-        <v>260.63</v>
+        <v>252.6</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K86" t="n">
+        <v>2568</v>
+      </c>
+      <c r="L86" t="n">
+        <v>117</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.575</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:38.989</t>
+          <t>2026-05-29 09:35:43.609</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779421721021</v>
+        <v>1780022141218</v>
       </c>
       <c r="C87" t="n">
-        <v>89002</v>
+        <v>88310</v>
       </c>
       <c r="D87" t="n">
-        <v>536.52</v>
+        <v>2778.5</v>
       </c>
       <c r="E87" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F87" t="n">
-        <v>765</v>
+        <v>7437</v>
       </c>
       <c r="G87" t="n">
-        <v>260.63</v>
+        <v>252.6</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>2391</v>
+      </c>
+      <c r="L87" t="n">
+        <v>103</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:38.990</t>
+          <t>2026-05-29 09:35:43.641</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779421721223</v>
+        <v>1780022141418</v>
       </c>
       <c r="C88" t="n">
-        <v>89124</v>
+        <v>87530</v>
       </c>
       <c r="D88" t="n">
-        <v>631.6900000000001</v>
+        <v>1859.58</v>
       </c>
       <c r="E88" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F88" t="n">
-        <v>765</v>
+        <v>7437</v>
       </c>
       <c r="G88" t="n">
-        <v>260.63</v>
+        <v>252.6</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K88" t="n">
+        <v>2222</v>
+      </c>
+      <c r="L88" t="n">
+        <v>109</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.469</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:39.570</t>
+          <t>2026-05-29 09:35:45.665</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779421721424</v>
+        <v>1780022141618</v>
       </c>
       <c r="C89" t="n">
-        <v>89260</v>
+        <v>89791</v>
       </c>
       <c r="D89" t="n">
-        <v>736.11</v>
+        <v>4027.6</v>
       </c>
       <c r="E89" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F89" t="n">
-        <v>725</v>
+        <v>7437</v>
       </c>
       <c r="G89" t="n">
-        <v>72.88</v>
+        <v>252.6</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K89" t="n">
+        <v>4046</v>
+      </c>
+      <c r="L89" t="n">
+        <v>107</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.882</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:39.571</t>
+          <t>2026-05-29 09:35:45.668</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779421721625</v>
+        <v>1780022141818</v>
       </c>
       <c r="C90" t="n">
-        <v>89284</v>
+        <v>93030</v>
       </c>
       <c r="D90" t="n">
-        <v>723.3</v>
+        <v>7065.22</v>
       </c>
       <c r="E90" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F90" t="n">
-        <v>725</v>
+        <v>7437</v>
       </c>
       <c r="G90" t="n">
-        <v>72.88</v>
+        <v>252.6</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>3849</v>
+      </c>
+      <c r="L90" t="n">
+        <v>108</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.042</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:39.571</t>
+          <t>2026-05-29 09:35:45.669</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779421721827</v>
+        <v>1780022142018</v>
       </c>
       <c r="C91" t="n">
-        <v>89069</v>
+        <v>86347</v>
       </c>
       <c r="D91" t="n">
-        <v>472.14</v>
+        <v>28.96</v>
       </c>
       <c r="E91" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F91" t="n">
-        <v>725</v>
+        <v>7437</v>
       </c>
       <c r="G91" t="n">
-        <v>72.88</v>
+        <v>252.6</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>3650</v>
+      </c>
+      <c r="L91" t="n">
+        <v>105</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.903</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:40.017</t>
+          <t>2026-05-29 09:35:45.670</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779421722028</v>
+        <v>1780022142218</v>
       </c>
       <c r="C92" t="n">
-        <v>89259</v>
+        <v>86433</v>
       </c>
       <c r="D92" t="n">
-        <v>638.53</v>
+        <v>113.51</v>
       </c>
       <c r="E92" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F92" t="n">
-        <v>725</v>
+        <v>7437</v>
       </c>
       <c r="G92" t="n">
-        <v>72.88</v>
+        <v>252.6</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K92" t="n">
+        <v>3451</v>
+      </c>
+      <c r="L92" t="n">
+        <v>115</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.079</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:40.023</t>
+          <t>2026-05-29 09:35:45.671</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779421722230</v>
+        <v>1780022142418</v>
       </c>
       <c r="C93" t="n">
-        <v>89482</v>
+        <v>86034</v>
       </c>
       <c r="D93" t="n">
-        <v>829.6</v>
+        <v>-291.17</v>
       </c>
       <c r="E93" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F93" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G93" t="n">
-        <v>76.83</v>
+        <v>252.6</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J93" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K93" t="n">
+        <v>3253</v>
+      </c>
+      <c r="L93" t="n">
+        <v>119</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.644</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:40.596</t>
+          <t>2026-05-29 09:35:45.673</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779421722431</v>
+        <v>1780022142758</v>
       </c>
       <c r="C94" t="n">
-        <v>89442</v>
+        <v>84454</v>
       </c>
       <c r="D94" t="n">
-        <v>748.12</v>
+        <v>-1856.61</v>
       </c>
       <c r="E94" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F94" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G94" t="n">
-        <v>76.83</v>
+        <v>252.6</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K94" t="n">
+        <v>2914</v>
+      </c>
+      <c r="L94" t="n">
+        <v>123</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.751</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:40.600</t>
+          <t>2026-05-29 09:35:45.674</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779421722632</v>
+        <v>1780022142958</v>
       </c>
       <c r="C95" t="n">
-        <v>89362</v>
+        <v>84043</v>
       </c>
       <c r="D95" t="n">
-        <v>630.72</v>
+        <v>-2174.78</v>
       </c>
       <c r="E95" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F95" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G95" t="n">
-        <v>76.83</v>
+        <v>252.6</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K95" t="n">
+        <v>2715</v>
+      </c>
+      <c r="L95" t="n">
+        <v>108</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.82</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:40.622</t>
+          <t>2026-05-29 09:35:45.676</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779421722834</v>
+        <v>1780022143177</v>
       </c>
       <c r="C96" t="n">
-        <v>89395</v>
+        <v>86731</v>
       </c>
       <c r="D96" t="n">
-        <v>632.1799999999999</v>
+        <v>621.96</v>
       </c>
       <c r="E96" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F96" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G96" t="n">
-        <v>76.83</v>
+        <v>252.6</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K96" t="n">
+        <v>2498</v>
+      </c>
+      <c r="L96" t="n">
+        <v>110</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.706</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:41.039</t>
+          <t>2026-05-29 09:35:45.677</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779421723035</v>
+        <v>1780022143377</v>
       </c>
       <c r="C97" t="n">
-        <v>89524</v>
+        <v>87522</v>
       </c>
       <c r="D97" t="n">
-        <v>729.5700000000001</v>
+        <v>1381.86</v>
       </c>
       <c r="E97" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F97" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G97" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>2299</v>
+      </c>
+      <c r="L97" t="n">
+        <v>115</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:41.045</t>
+          <t>2026-05-29 09:35:45.678</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779421723237</v>
+        <v>1780022143577</v>
       </c>
       <c r="C98" t="n">
-        <v>89321</v>
+        <v>87131</v>
       </c>
       <c r="D98" t="n">
-        <v>490.09</v>
+        <v>921.77</v>
       </c>
       <c r="E98" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F98" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G98" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>2100</v>
+      </c>
+      <c r="L98" t="n">
+        <v>108</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.377</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:41.429</t>
+          <t>2026-05-29 09:35:45.680</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779421723438</v>
+        <v>1780022143777</v>
       </c>
       <c r="C99" t="n">
-        <v>89194</v>
+        <v>87366</v>
       </c>
       <c r="D99" t="n">
-        <v>338.59</v>
+        <v>1110.68</v>
       </c>
       <c r="E99" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F99" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G99" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1902</v>
+      </c>
+      <c r="L99" t="n">
+        <v>111</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.246</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:41.430</t>
+          <t>2026-05-29 09:35:46.566</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779421723639</v>
+        <v>1780022143977</v>
       </c>
       <c r="C100" t="n">
-        <v>89185</v>
+        <v>86282</v>
       </c>
       <c r="D100" t="n">
-        <v>312.66</v>
+        <v>-28.85</v>
       </c>
       <c r="E100" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F100" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G100" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K100" t="n">
+        <v>2588</v>
+      </c>
+      <c r="L100" t="n">
+        <v>109</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.087</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:41.861</t>
+          <t>2026-05-29 09:35:46.568</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779421723841</v>
+        <v>1780022144177</v>
       </c>
       <c r="C101" t="n">
-        <v>89235</v>
+        <v>86078</v>
       </c>
       <c r="D101" t="n">
-        <v>347.03</v>
+        <v>-231.41</v>
       </c>
       <c r="E101" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F101" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G101" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J101" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K101" t="n">
+        <v>2390</v>
+      </c>
+      <c r="L101" t="n">
+        <v>112</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.069</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:41.862</t>
+          <t>2026-05-29 09:35:46.570</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779421724042</v>
+        <v>1780022144377</v>
       </c>
       <c r="C102" t="n">
-        <v>88656</v>
+        <v>85917</v>
       </c>
       <c r="D102" t="n">
-        <v>-249.33</v>
+        <v>-380.84</v>
       </c>
       <c r="E102" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F102" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G102" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K102" t="n">
+        <v>2191</v>
+      </c>
+      <c r="L102" t="n">
+        <v>108</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1.371</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:42.359</t>
+          <t>2026-05-29 09:35:46.571</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779421724244</v>
+        <v>1780022144797</v>
       </c>
       <c r="C103" t="n">
-        <v>89011</v>
+        <v>85647</v>
       </c>
       <c r="D103" t="n">
-        <v>118.14</v>
+        <v>-631.8</v>
       </c>
       <c r="E103" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F103" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G103" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1773</v>
+      </c>
+      <c r="L103" t="n">
+        <v>124</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.209</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:42.360</t>
+          <t>2026-05-29 09:35:46.573</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779421724445</v>
+        <v>1780022144997</v>
       </c>
       <c r="C104" t="n">
-        <v>89278</v>
+        <v>85531</v>
       </c>
       <c r="D104" t="n">
-        <v>379.23</v>
+        <v>-716.21</v>
       </c>
       <c r="E104" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F104" t="n">
-        <v>806</v>
+        <v>7437</v>
       </c>
       <c r="G104" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1574</v>
+      </c>
+      <c r="L104" t="n">
+        <v>108</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.301</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:42.643</t>
+          <t>2026-05-29 09:35:46.574</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779421724646</v>
+        <v>1780022145198</v>
       </c>
       <c r="C105" t="n">
-        <v>89316</v>
+        <v>85053</v>
       </c>
       <c r="D105" t="n">
-        <v>398.27</v>
+        <v>-1158.4</v>
       </c>
       <c r="E105" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F105" t="n">
-        <v>1530</v>
+        <v>7437</v>
       </c>
       <c r="G105" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L105" t="n">
+        <v>109</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.236</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:42.644</t>
+          <t>2026-05-29 09:35:46.776</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779421724848</v>
+        <v>1780022145416</v>
       </c>
       <c r="C106" t="n">
-        <v>89038</v>
+        <v>85533</v>
       </c>
       <c r="D106" t="n">
-        <v>100.36</v>
+        <v>-620.48</v>
       </c>
       <c r="E106" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F106" t="n">
-        <v>1530</v>
+        <v>7437</v>
       </c>
       <c r="G106" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1358</v>
+      </c>
+      <c r="L106" t="n">
+        <v>118</v>
+      </c>
+      <c r="M106" t="n">
+        <v>2.346</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:43.082</t>
+          <t>2026-05-29 09:35:46.777</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779421725049</v>
+        <v>1780022145616</v>
       </c>
       <c r="C107" t="n">
-        <v>89297</v>
+        <v>86272</v>
       </c>
       <c r="D107" t="n">
-        <v>354.34</v>
+        <v>149.55</v>
       </c>
       <c r="E107" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F107" t="n">
-        <v>1530</v>
+        <v>7437</v>
       </c>
       <c r="G107" t="n">
-        <v>79.13</v>
+        <v>252.6</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1161</v>
+      </c>
+      <c r="L107" t="n">
+        <v>112</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.819</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:43.088</t>
+          <t>2026-05-29 09:35:46.936</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779421725251</v>
+        <v>1780022145817</v>
       </c>
       <c r="C108" t="n">
-        <v>89485</v>
+        <v>87217</v>
       </c>
       <c r="D108" t="n">
-        <v>524.62</v>
+        <v>1087.07</v>
       </c>
       <c r="E108" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F108" t="n">
-        <v>685</v>
+        <v>7437</v>
       </c>
       <c r="G108" t="n">
-        <v>77.41</v>
+        <v>252.6</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1118</v>
+      </c>
+      <c r="L108" t="n">
+        <v>105</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.353</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:43.535</t>
+          <t>2026-05-29 09:35:47.050</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779421725452</v>
+        <v>1780022146016</v>
       </c>
       <c r="C109" t="n">
-        <v>89090</v>
+        <v>88026</v>
       </c>
       <c r="D109" t="n">
-        <v>103.39</v>
+        <v>1841.72</v>
       </c>
       <c r="E109" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F109" t="n">
-        <v>685</v>
+        <v>7437</v>
       </c>
       <c r="G109" t="n">
-        <v>77.41</v>
+        <v>252.6</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1033</v>
+      </c>
+      <c r="L109" t="n">
+        <v>121</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.36</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:43.566</t>
+          <t>2026-05-29 09:35:47.623</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779421725653</v>
+        <v>1780022146217</v>
       </c>
       <c r="C110" t="n">
-        <v>89096</v>
+        <v>87539</v>
       </c>
       <c r="D110" t="n">
-        <v>104.22</v>
+        <v>1262.63</v>
       </c>
       <c r="E110" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F110" t="n">
-        <v>685</v>
+        <v>7437</v>
       </c>
       <c r="G110" t="n">
-        <v>77.41</v>
+        <v>252.6</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1405</v>
+      </c>
+      <c r="L110" t="n">
+        <v>106</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.787</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:44.181</t>
+          <t>2026-05-29 09:35:47.624</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779421725855</v>
+        <v>1780022146416</v>
       </c>
       <c r="C111" t="n">
-        <v>89582</v>
+        <v>87980</v>
       </c>
       <c r="D111" t="n">
-        <v>585.01</v>
+        <v>1640.5</v>
       </c>
       <c r="E111" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F111" t="n">
-        <v>685</v>
+        <v>7437</v>
       </c>
       <c r="G111" t="n">
-        <v>77.41</v>
+        <v>252.6</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1207</v>
+      </c>
+      <c r="L111" t="n">
+        <v>118</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.652</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:44.186</t>
+          <t>2026-05-29 09:35:47.625</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779421726056</v>
+        <v>1780022146616</v>
       </c>
       <c r="C112" t="n">
-        <v>89966</v>
+        <v>87972</v>
       </c>
       <c r="D112" t="n">
-        <v>939.76</v>
+        <v>1550.47</v>
       </c>
       <c r="E112" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F112" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G112" t="n">
-        <v>78.53</v>
+        <v>252.6</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1008</v>
+      </c>
+      <c r="L112" t="n">
+        <v>111</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.598</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:44.219</t>
+          <t>2026-05-29 09:35:48.110</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779421726258</v>
+        <v>1780022146816</v>
       </c>
       <c r="C113" t="n">
-        <v>89788</v>
+        <v>88126</v>
       </c>
       <c r="D113" t="n">
-        <v>714.77</v>
+        <v>1626.95</v>
       </c>
       <c r="E113" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F113" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G113" t="n">
-        <v>78.53</v>
+        <v>252.6</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1293</v>
+      </c>
+      <c r="L113" t="n">
+        <v>116</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.286</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:44.220</t>
+          <t>2026-05-29 09:35:48.181</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779421726459</v>
+        <v>1780022147016</v>
       </c>
       <c r="C114" t="n">
-        <v>89913</v>
+        <v>86910</v>
       </c>
       <c r="D114" t="n">
-        <v>804.03</v>
+        <v>329.6</v>
       </c>
       <c r="E114" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F114" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G114" t="n">
-        <v>78.53</v>
+        <v>252.6</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1164</v>
+      </c>
+      <c r="L114" t="n">
+        <v>104</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.415</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:44.497</t>
+          <t>2026-05-29 09:35:48.184</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779421726660</v>
+        <v>1780022147216</v>
       </c>
       <c r="C115" t="n">
-        <v>90048</v>
+        <v>86014</v>
       </c>
       <c r="D115" t="n">
-        <v>898.83</v>
+        <v>-582.88</v>
       </c>
       <c r="E115" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F115" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G115" t="n">
-        <v>78.53</v>
+        <v>252.6</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K115" t="n">
+        <v>967</v>
+      </c>
+      <c r="L115" t="n">
+        <v>106</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.671</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:44.909</t>
+          <t>2026-05-29 09:35:48.483</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779421726862</v>
+        <v>1780022147416</v>
       </c>
       <c r="C116" t="n">
-        <v>89596</v>
+        <v>85444</v>
       </c>
       <c r="D116" t="n">
-        <v>401.89</v>
+        <v>-1123.73</v>
       </c>
       <c r="E116" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F116" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G116" t="n">
-        <v>78.53</v>
+        <v>252.6</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1066</v>
+      </c>
+      <c r="L116" t="n">
+        <v>116</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.175</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:44.910</t>
+          <t>2026-05-29 09:35:48.484</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779421727063</v>
+        <v>1780022147616</v>
       </c>
       <c r="C117" t="n">
-        <v>89845</v>
+        <v>85861</v>
       </c>
       <c r="D117" t="n">
-        <v>630.8</v>
+        <v>-650.55</v>
       </c>
       <c r="E117" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F117" t="n">
-        <v>785</v>
+        <v>7437</v>
       </c>
       <c r="G117" t="n">
-        <v>78.53</v>
+        <v>252.6</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K117" t="n">
+        <v>867</v>
+      </c>
+      <c r="L117" t="n">
+        <v>112</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.966</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:45.310</t>
+          <t>2026-05-29 09:35:49.457</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779421727265</v>
+        <v>1780022147835</v>
       </c>
       <c r="C118" t="n">
-        <v>89948</v>
+        <v>86696</v>
       </c>
       <c r="D118" t="n">
-        <v>702.26</v>
+        <v>216.98</v>
       </c>
       <c r="E118" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F118" t="n">
-        <v>1330</v>
+        <v>7437</v>
       </c>
       <c r="G118" t="n">
-        <v>204.73</v>
+        <v>252.6</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1621</v>
+      </c>
+      <c r="L118" t="n">
+        <v>113</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.423</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:45.311</t>
+          <t>2026-05-29 09:35:49.480</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779421727466</v>
+        <v>1780022148035</v>
       </c>
       <c r="C119" t="n">
-        <v>89923</v>
+        <v>86900</v>
       </c>
       <c r="D119" t="n">
-        <v>642.14</v>
+        <v>410.13</v>
       </c>
       <c r="E119" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F119" t="n">
-        <v>1330</v>
+        <v>7437</v>
       </c>
       <c r="G119" t="n">
-        <v>204.73</v>
+        <v>252.6</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1445</v>
+      </c>
+      <c r="L119" t="n">
+        <v>108</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.546</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:45.775</t>
+          <t>2026-05-29 09:35:50.160</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779421727667</v>
+        <v>1780022148235</v>
       </c>
       <c r="C120" t="n">
-        <v>89555</v>
+        <v>86335</v>
       </c>
       <c r="D120" t="n">
-        <v>242.04</v>
+        <v>-175.38</v>
       </c>
       <c r="E120" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F120" t="n">
-        <v>1330</v>
+        <v>7437</v>
       </c>
       <c r="G120" t="n">
-        <v>204.73</v>
+        <v>252.6</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1923</v>
+      </c>
+      <c r="L120" t="n">
+        <v>112</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.393</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:45.776</t>
+          <t>2026-05-29 09:35:50.161</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779421727869</v>
+        <v>1780022148435</v>
       </c>
       <c r="C121" t="n">
-        <v>89711</v>
+        <v>85011</v>
       </c>
       <c r="D121" t="n">
-        <v>385.93</v>
+        <v>-1490.61</v>
       </c>
       <c r="E121" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F121" t="n">
-        <v>1330</v>
+        <v>7437</v>
       </c>
       <c r="G121" t="n">
-        <v>204.73</v>
+        <v>252.6</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1725</v>
+      </c>
+      <c r="L121" t="n">
+        <v>115</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.981</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:46.128</t>
+          <t>2026-05-29 09:35:50.162</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779421728070</v>
+        <v>1780022148635</v>
       </c>
       <c r="C122" t="n">
-        <v>89927</v>
+        <v>84368</v>
       </c>
       <c r="D122" t="n">
-        <v>582.64</v>
+        <v>-2059.08</v>
       </c>
       <c r="E122" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F122" t="n">
-        <v>805</v>
+        <v>7437</v>
       </c>
       <c r="G122" t="n">
-        <v>194.07</v>
+        <v>252.6</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1526</v>
+      </c>
+      <c r="L122" t="n">
+        <v>112</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.991</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:46.129</t>
+          <t>2026-05-29 09:35:50.164</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779421728272</v>
+        <v>1780022148835</v>
       </c>
       <c r="C123" t="n">
-        <v>89564</v>
+        <v>81958</v>
       </c>
       <c r="D123" t="n">
-        <v>190.51</v>
+        <v>-4366.12</v>
       </c>
       <c r="E123" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F123" t="n">
-        <v>805</v>
+        <v>7437</v>
       </c>
       <c r="G123" t="n">
-        <v>194.07</v>
+        <v>252.6</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1327</v>
+      </c>
+      <c r="L123" t="n">
+        <v>107</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.423</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:46.540</t>
+          <t>2026-05-29 09:35:50.889</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779421728473</v>
+        <v>1780022149035</v>
       </c>
       <c r="C124" t="n">
-        <v>89655</v>
+        <v>80710</v>
       </c>
       <c r="D124" t="n">
-        <v>271.98</v>
+        <v>-5395.82</v>
       </c>
       <c r="E124" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F124" t="n">
-        <v>805</v>
+        <v>7437</v>
       </c>
       <c r="G124" t="n">
-        <v>194.07</v>
+        <v>252.6</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1852</v>
+      </c>
+      <c r="L124" t="n">
+        <v>113</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.817</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:46.541</t>
+          <t>2026-05-29 09:35:50.892</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779421728674</v>
+        <v>1780022149235</v>
       </c>
       <c r="C125" t="n">
-        <v>89767</v>
+        <v>79956</v>
       </c>
       <c r="D125" t="n">
-        <v>370.38</v>
+        <v>-5880.03</v>
       </c>
       <c r="E125" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F125" t="n">
-        <v>805</v>
+        <v>7437</v>
       </c>
       <c r="G125" t="n">
-        <v>194.07</v>
+        <v>252.6</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1657</v>
+      </c>
+      <c r="L125" t="n">
+        <v>117</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.668</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:46.751</t>
+          <t>2026-05-29 09:35:50.894</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779421728876</v>
+        <v>1780022149435</v>
       </c>
       <c r="C126" t="n">
-        <v>89903</v>
+        <v>80570</v>
       </c>
       <c r="D126" t="n">
-        <v>487.86</v>
+        <v>-4972.02</v>
       </c>
       <c r="E126" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F126" t="n">
-        <v>745</v>
+        <v>7437</v>
       </c>
       <c r="G126" t="n">
-        <v>182.22</v>
+        <v>252.6</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1458</v>
+      </c>
+      <c r="L126" t="n">
+        <v>109</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.263</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:47.157</t>
+          <t>2026-05-29 09:35:50.895</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779421729077</v>
+        <v>1780022149635</v>
       </c>
       <c r="C127" t="n">
-        <v>89762</v>
+        <v>81463</v>
       </c>
       <c r="D127" t="n">
-        <v>322.47</v>
+        <v>-3830.42</v>
       </c>
       <c r="E127" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F127" t="n">
-        <v>745</v>
+        <v>7437</v>
       </c>
       <c r="G127" t="n">
-        <v>182.22</v>
+        <v>252.6</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1260</v>
+      </c>
+      <c r="L127" t="n">
+        <v>113</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:47.213</t>
+          <t>2026-05-29 09:35:51.248</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779421729278</v>
+        <v>1780022149835</v>
       </c>
       <c r="C128" t="n">
-        <v>89628</v>
+        <v>81935</v>
       </c>
       <c r="D128" t="n">
-        <v>172.35</v>
+        <v>-3166.9</v>
       </c>
       <c r="E128" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F128" t="n">
-        <v>745</v>
+        <v>7437</v>
       </c>
       <c r="G128" t="n">
-        <v>182.22</v>
+        <v>252.6</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1412</v>
+      </c>
+      <c r="L128" t="n">
+        <v>114</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.679</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:47.625</t>
+          <t>2026-05-29 09:35:51.248</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779421729480</v>
+        <v>1780022150035</v>
       </c>
       <c r="C129" t="n">
-        <v>89643</v>
+        <v>82345</v>
       </c>
       <c r="D129" t="n">
-        <v>178.73</v>
+        <v>-2598.56</v>
       </c>
       <c r="E129" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F129" t="n">
-        <v>745</v>
+        <v>7437</v>
       </c>
       <c r="G129" t="n">
-        <v>182.22</v>
+        <v>252.6</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1213</v>
+      </c>
+      <c r="L129" t="n">
+        <v>117</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.525</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:47.626</t>
+          <t>2026-05-29 09:35:51.249</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779421729681</v>
+        <v>1780022150254</v>
       </c>
       <c r="C130" t="n">
-        <v>89719</v>
+        <v>82062</v>
       </c>
       <c r="D130" t="n">
-        <v>245.79</v>
+        <v>-2751.63</v>
       </c>
       <c r="E130" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F130" t="n">
-        <v>745</v>
+        <v>7437</v>
       </c>
       <c r="G130" t="n">
-        <v>182.22</v>
+        <v>252.6</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K130" t="n">
+        <v>994</v>
+      </c>
+      <c r="L130" t="n">
+        <v>111</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.487</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:48.018</t>
+          <t>2026-05-29 09:35:51.249</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779421729883</v>
+        <v>1780022150454</v>
       </c>
       <c r="C131" t="n">
-        <v>89693</v>
+        <v>82113</v>
       </c>
       <c r="D131" t="n">
-        <v>207.5</v>
+        <v>-2563.05</v>
       </c>
       <c r="E131" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F131" t="n">
-        <v>1007</v>
+        <v>7437</v>
       </c>
       <c r="G131" t="n">
-        <v>190.35</v>
+        <v>252.6</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K131" t="n">
+        <v>795</v>
+      </c>
+      <c r="L131" t="n">
+        <v>108</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.494</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 10:48:48.024</t>
+          <t>2026-05-29 09:35:57.064</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779421730084</v>
+        <v>1780022150654</v>
       </c>
       <c r="C132" t="n">
-        <v>89514</v>
+        <v>82166</v>
       </c>
       <c r="D132" t="n">
-        <v>18.13</v>
+        <v>-2381.9</v>
       </c>
       <c r="E132" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F132" t="n">
-        <v>1007</v>
+        <v>7437</v>
       </c>
       <c r="G132" t="n">
-        <v>190.35</v>
+        <v>252.6</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:48.391</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>1779421730285</v>
-      </c>
-      <c r="C133" t="n">
-        <v>89684</v>
-      </c>
-      <c r="D133" t="n">
-        <v>187.22</v>
-      </c>
-      <c r="E133" t="n">
-        <v>64</v>
-      </c>
-      <c r="F133" t="n">
-        <v>1007</v>
-      </c>
-      <c r="G133" t="n">
-        <v>190.35</v>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:48.392</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>1779421730487</v>
-      </c>
-      <c r="C134" t="n">
-        <v>89818</v>
-      </c>
-      <c r="D134" t="n">
-        <v>311.86</v>
-      </c>
-      <c r="E134" t="n">
-        <v>78</v>
-      </c>
-      <c r="F134" t="n">
-        <v>584</v>
-      </c>
-      <c r="G134" t="n">
-        <v>206.79</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:48.801</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>1779421730688</v>
-      </c>
-      <c r="C135" t="n">
-        <v>89730</v>
-      </c>
-      <c r="D135" t="n">
-        <v>208.27</v>
-      </c>
-      <c r="E135" t="n">
-        <v>78</v>
-      </c>
-      <c r="F135" t="n">
-        <v>584</v>
-      </c>
-      <c r="G135" t="n">
-        <v>206.79</v>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:48.851</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>1779421730890</v>
-      </c>
-      <c r="C136" t="n">
-        <v>89409</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-123.15</v>
-      </c>
-      <c r="E136" t="n">
-        <v>78</v>
-      </c>
-      <c r="F136" t="n">
-        <v>584</v>
-      </c>
-      <c r="G136" t="n">
-        <v>206.79</v>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:49.199</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>1779421731091</v>
-      </c>
-      <c r="C137" t="n">
-        <v>89544</v>
-      </c>
-      <c r="D137" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="E137" t="n">
-        <v>78</v>
-      </c>
-      <c r="F137" t="n">
-        <v>584</v>
-      </c>
-      <c r="G137" t="n">
-        <v>206.79</v>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:49.199</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>1779421731292</v>
-      </c>
-      <c r="C138" t="n">
-        <v>89710</v>
-      </c>
-      <c r="D138" t="n">
-        <v>183.11</v>
-      </c>
-      <c r="E138" t="n">
-        <v>78</v>
-      </c>
-      <c r="F138" t="n">
-        <v>584</v>
-      </c>
-      <c r="G138" t="n">
-        <v>206.79</v>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:49.829</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>1779421731494</v>
-      </c>
-      <c r="C139" t="n">
-        <v>89970</v>
-      </c>
-      <c r="D139" t="n">
-        <v>433.95</v>
-      </c>
-      <c r="E139" t="n">
-        <v>76</v>
-      </c>
-      <c r="F139" t="n">
-        <v>927</v>
-      </c>
-      <c r="G139" t="n">
-        <v>205.5</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:49.833</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>1779421731695</v>
-      </c>
-      <c r="C140" t="n">
-        <v>89469</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-88.73999999999999</v>
-      </c>
-      <c r="E140" t="n">
-        <v>76</v>
-      </c>
-      <c r="F140" t="n">
-        <v>927</v>
-      </c>
-      <c r="G140" t="n">
-        <v>205.5</v>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:49.854</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>1779421731897</v>
-      </c>
-      <c r="C141" t="n">
-        <v>89583</v>
-      </c>
-      <c r="D141" t="n">
-        <v>29.69</v>
-      </c>
-      <c r="E141" t="n">
-        <v>76</v>
-      </c>
-      <c r="F141" t="n">
-        <v>927</v>
-      </c>
-      <c r="G141" t="n">
-        <v>205.5</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:49.855</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1779421732098</v>
-      </c>
-      <c r="C142" t="n">
-        <v>89726</v>
-      </c>
-      <c r="D142" t="n">
-        <v>171.21</v>
-      </c>
-      <c r="E142" t="n">
-        <v>76</v>
-      </c>
-      <c r="F142" t="n">
-        <v>927</v>
-      </c>
-      <c r="G142" t="n">
-        <v>205.5</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:50.465</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1779421732299</v>
-      </c>
-      <c r="C143" t="n">
-        <v>89841</v>
-      </c>
-      <c r="D143" t="n">
-        <v>277.65</v>
-      </c>
-      <c r="E143" t="n">
-        <v>73</v>
-      </c>
-      <c r="F143" t="n">
-        <v>846</v>
-      </c>
-      <c r="G143" t="n">
-        <v>204.98</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:50.478</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>1779421732501</v>
-      </c>
-      <c r="C144" t="n">
-        <v>89387</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-190.23</v>
-      </c>
-      <c r="E144" t="n">
-        <v>73</v>
-      </c>
-      <c r="F144" t="n">
-        <v>846</v>
-      </c>
-      <c r="G144" t="n">
-        <v>204.98</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:50.846</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1779421732702</v>
-      </c>
-      <c r="C145" t="n">
-        <v>89477</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-90.72</v>
-      </c>
-      <c r="E145" t="n">
-        <v>73</v>
-      </c>
-      <c r="F145" t="n">
-        <v>846</v>
-      </c>
-      <c r="G145" t="n">
-        <v>204.98</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:50.847</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1779421732904</v>
-      </c>
-      <c r="C146" t="n">
-        <v>89671</v>
-      </c>
-      <c r="D146" t="n">
-        <v>107.81</v>
-      </c>
-      <c r="E146" t="n">
-        <v>73</v>
-      </c>
-      <c r="F146" t="n">
-        <v>846</v>
-      </c>
-      <c r="G146" t="n">
-        <v>204.98</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:50.848</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1779421733105</v>
-      </c>
-      <c r="C147" t="n">
-        <v>89838</v>
-      </c>
-      <c r="D147" t="n">
-        <v>269.42</v>
-      </c>
-      <c r="E147" t="n">
-        <v>76</v>
-      </c>
-      <c r="F147" t="n">
-        <v>845</v>
-      </c>
-      <c r="G147" t="n">
-        <v>204.38</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:51.324</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>1779421733306</v>
-      </c>
-      <c r="C148" t="n">
-        <v>89666</v>
-      </c>
-      <c r="D148" t="n">
-        <v>83.95</v>
-      </c>
-      <c r="E148" t="n">
-        <v>76</v>
-      </c>
-      <c r="F148" t="n">
-        <v>845</v>
-      </c>
-      <c r="G148" t="n">
-        <v>204.38</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:51.358</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1779421733508</v>
-      </c>
-      <c r="C149" t="n">
-        <v>89808</v>
-      </c>
-      <c r="D149" t="n">
-        <v>221.75</v>
-      </c>
-      <c r="E149" t="n">
-        <v>76</v>
-      </c>
-      <c r="F149" t="n">
-        <v>845</v>
-      </c>
-      <c r="G149" t="n">
-        <v>204.38</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:51.564</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1779421733709</v>
-      </c>
-      <c r="C150" t="n">
-        <v>90115</v>
-      </c>
-      <c r="D150" t="n">
-        <v>517.67</v>
-      </c>
-      <c r="E150" t="n">
-        <v>73</v>
-      </c>
-      <c r="F150" t="n">
-        <v>665</v>
-      </c>
-      <c r="G150" t="n">
-        <v>206.32</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:51.881</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1779421733911</v>
-      </c>
-      <c r="C151" t="n">
-        <v>90225</v>
-      </c>
-      <c r="D151" t="n">
-        <v>601.78</v>
-      </c>
-      <c r="E151" t="n">
-        <v>73</v>
-      </c>
-      <c r="F151" t="n">
-        <v>665</v>
-      </c>
-      <c r="G151" t="n">
-        <v>206.32</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:51.902</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1779421734112</v>
-      </c>
-      <c r="C152" t="n">
-        <v>89830</v>
-      </c>
-      <c r="D152" t="n">
-        <v>176.69</v>
-      </c>
-      <c r="E152" t="n">
-        <v>73</v>
-      </c>
-      <c r="F152" t="n">
-        <v>665</v>
-      </c>
-      <c r="G152" t="n">
-        <v>206.32</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:52.285</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>1779421734313</v>
-      </c>
-      <c r="C153" t="n">
-        <v>89672</v>
-      </c>
-      <c r="D153" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="E153" t="n">
-        <v>73</v>
-      </c>
-      <c r="F153" t="n">
-        <v>665</v>
-      </c>
-      <c r="G153" t="n">
-        <v>206.32</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:52.296</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>1779421734515</v>
-      </c>
-      <c r="C154" t="n">
-        <v>89522</v>
-      </c>
-      <c r="D154" t="n">
-        <v>-140.63</v>
-      </c>
-      <c r="E154" t="n">
-        <v>73</v>
-      </c>
-      <c r="F154" t="n">
-        <v>665</v>
-      </c>
-      <c r="G154" t="n">
-        <v>206.32</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:48:53.110</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>1779421734716</v>
-      </c>
-      <c r="C155" t="n">
-        <v>89546</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-109.6</v>
-      </c>
-      <c r="E155" t="n">
-        <v>73</v>
-      </c>
-      <c r="F155" t="n">
-        <v>665</v>
-      </c>
-      <c r="G155" t="n">
-        <v>206.32</v>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I132" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K132" t="n">
+        <v>6409</v>
+      </c>
+      <c r="L132" t="n">
+        <v>114</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
